--- a/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
+++ b/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\School\Desktop\repos\DAQ\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\School\Documents\repos\DAQ\daq_system\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B94C24C-E5A6-4CEF-8EB9-7D6F65B94D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B03EB84-9881-45A5-98DD-BF241FDD55D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12720" yWindow="0" windowWidth="12960" windowHeight="15360" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67" yWindow="413" windowWidth="12733" windowHeight="15520" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="110">
   <si>
     <t>Name</t>
   </si>
@@ -333,12 +333,6 @@
   </si>
   <si>
     <t>Dev5/ai22</t>
-  </si>
-  <si>
-    <t>Dev5/ai21</t>
-  </si>
-  <si>
-    <t>PT-HE-201</t>
   </si>
   <si>
     <t>DI-6</t>
@@ -980,7 +974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultColWidth="21.29296875" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="14.703125" style="2" customWidth="1"/>
@@ -1053,7 +1047,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>44</v>
@@ -1093,7 +1087,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>44</v>
@@ -1133,7 +1127,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>44</v>
@@ -1173,7 +1167,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>44</v>
@@ -1214,7 +1208,7 @@
         <v>17</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>44</v>
@@ -1254,7 +1248,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>44</v>
@@ -1294,7 +1288,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>44</v>
@@ -1334,7 +1328,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>44</v>
@@ -1374,7 +1368,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>44</v>
@@ -1413,7 +1407,7 @@
         <v>17</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>44</v>
@@ -1452,7 +1446,7 @@
         <v>17</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>44</v>
@@ -1488,7 +1482,7 @@
         <v>17</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>44</v>
@@ -1524,7 +1518,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>44</v>
@@ -1560,7 +1554,7 @@
         <v>17</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>44</v>
@@ -1593,7 +1587,7 @@
         <v>17</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>44</v>
@@ -1614,52 +1608,16 @@
       <c r="N16" s="14"/>
       <c r="O16" s="14"/>
       <c r="P16" s="14"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="14">
-        <v>499.70649495375898</v>
-      </c>
-      <c r="G17" s="15">
-        <v>-3.51061102707081</v>
-      </c>
-      <c r="H17" s="15">
-        <v>0</v>
-      </c>
-      <c r="I17" s="15">
-        <v>10</v>
-      </c>
-      <c r="J17" s="15">
-        <v>14.9</v>
-      </c>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="M1:P1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E18:E291 E5:E16" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17:E290 E5:E16" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"default,RSE,NRSE,Differential,Pseudodifferential"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18:C291 C5:C16" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C290 C5:C16" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"no,yes"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2553,7 +2511,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
@@ -2597,7 +2555,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
         <v>83</v>
@@ -2608,7 +2566,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B9" t="s">
         <v>84</v>
@@ -2619,7 +2577,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s">
         <v>85</v>
@@ -2630,7 +2588,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
         <v>86</v>
@@ -2641,7 +2599,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
@@ -2652,7 +2610,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s">
         <v>89</v>

--- a/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
+++ b/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\School\Documents\repos\DAQ\daq_system\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B03EB84-9881-45A5-98DD-BF241FDD55D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF601555-DFC4-48D3-A6C4-5D939B4A6763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67" yWindow="413" windowWidth="12733" windowHeight="15520" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12800" yWindow="413" windowWidth="12733" windowHeight="15520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="106">
   <si>
     <t>Name</t>
   </si>
@@ -311,18 +311,6 @@
     <t>FMS</t>
   </si>
   <si>
-    <t>Dev5/ai19</t>
-  </si>
-  <si>
-    <t>Dev5/ai20</t>
-  </si>
-  <si>
-    <t>PT-FU-202</t>
-  </si>
-  <si>
-    <t>PT-OX-202</t>
-  </si>
-  <si>
     <t>RTD-FU</t>
   </si>
   <si>
@@ -338,12 +326,6 @@
     <t>DI-6</t>
   </si>
   <si>
-    <t>DI-9</t>
-  </si>
-  <si>
-    <t>DI-11</t>
-  </si>
-  <si>
     <t>REED-OX-MAROTTA</t>
   </si>
   <si>
@@ -360,6 +342,12 @@
   </si>
   <si>
     <t>Pounds</t>
+  </si>
+  <si>
+    <t>DI-03</t>
+  </si>
+  <si>
+    <t>DI-1</t>
   </si>
 </sst>
 </file>
@@ -974,7 +962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="21.29296875" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="14.703125" style="2" customWidth="1"/>
@@ -1047,7 +1035,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>44</v>
@@ -1087,7 +1075,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>44</v>
@@ -1127,7 +1115,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>44</v>
@@ -1167,7 +1155,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>44</v>
@@ -1208,7 +1196,7 @@
         <v>17</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>44</v>
@@ -1248,7 +1236,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>44</v>
@@ -1288,7 +1276,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>44</v>
@@ -1328,7 +1316,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>44</v>
@@ -1368,7 +1356,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>44</v>
@@ -1407,7 +1395,7 @@
         <v>17</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>44</v>
@@ -1446,7 +1434,7 @@
         <v>17</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>44</v>
@@ -1473,34 +1461,34 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A13" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>106</v>
+      <c r="D13" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="2">
-        <v>299.727093171143</v>
-      </c>
-      <c r="G13" s="2">
-        <v>-5.2730520568402</v>
-      </c>
-      <c r="H13" s="14">
+      <c r="F13" s="14">
+        <v>1</v>
+      </c>
+      <c r="G13" s="15">
         <v>0</v>
       </c>
+      <c r="H13" s="15">
+        <v>0</v>
+      </c>
       <c r="I13" s="15">
-        <v>10</v>
-      </c>
-      <c r="J13" s="14">
-        <v>14.9</v>
+        <v>5</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0</v>
       </c>
       <c r="M13" s="14"/>
       <c r="N13" s="14"/>
@@ -1509,115 +1497,49 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>94</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>106</v>
+      <c r="D14" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="2">
-        <v>300.40325697386402</v>
-      </c>
-      <c r="G14" s="2">
-        <v>2.0020088120354602</v>
-      </c>
-      <c r="H14" s="14">
+      <c r="F14" s="14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="15">
         <v>0</v>
       </c>
+      <c r="H14" s="15">
+        <v>0</v>
+      </c>
       <c r="I14" s="15">
-        <v>10</v>
-      </c>
-      <c r="J14" s="14">
-        <v>14.9</v>
+        <v>5</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0</v>
       </c>
       <c r="M14" s="14"/>
       <c r="N14" s="14"/>
       <c r="O14" s="14"/>
       <c r="P14" s="14"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.5">
-      <c r="A15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>0</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
-      </c>
-      <c r="I15" s="15">
-        <v>5</v>
-      </c>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.5">
-      <c r="A16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="14">
-        <v>1</v>
-      </c>
-      <c r="G16" s="15">
-        <v>0</v>
-      </c>
-      <c r="H16" s="15">
-        <v>0</v>
-      </c>
-      <c r="I16" s="15">
-        <v>5</v>
-      </c>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="M1:P1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17:E290 E5:E16" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E288" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"default,RSE,NRSE,Differential,Pseudodifferential"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C290 C5:C16" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C288" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"no,yes"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2492,7 +2414,7 @@
         <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>17</v>
@@ -2503,7 +2425,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -2525,7 +2447,7 @@
         <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -2555,7 +2477,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
         <v>83</v>
@@ -2566,7 +2488,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
         <v>84</v>
@@ -2577,10 +2499,10 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -2588,10 +2510,10 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -2610,10 +2532,10 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>

--- a/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
+++ b/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\School\Documents\repos\DAQ\daq_system\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\School\Documents\data_gather\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF601555-DFC4-48D3-A6C4-5D939B4A6763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE3D888-3C9D-4681-816C-F704F57AC41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12800" yWindow="413" windowWidth="12733" windowHeight="15520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13" yWindow="0" windowWidth="25587" windowHeight="15267" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="110">
   <si>
     <t>Name</t>
   </si>
@@ -348,6 +348,18 @@
   </si>
   <si>
     <t>DI-1</t>
+  </si>
+  <si>
+    <t>PT-FU-202</t>
+  </si>
+  <si>
+    <t>Dev5/ai19</t>
+  </si>
+  <si>
+    <t>PT-OX-202</t>
+  </si>
+  <si>
+    <t>Dev5/ai20</t>
   </si>
 </sst>
 </file>
@@ -962,7 +974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultColWidth="21.29296875" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="14.703125" style="2" customWidth="1"/>
@@ -1531,15 +1543,87 @@
       <c r="O14" s="14"/>
       <c r="P14" s="14"/>
     </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="2">
+        <v>299.727093171143</v>
+      </c>
+      <c r="G15" s="2">
+        <v>-5.2730520568402</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
+        <v>10</v>
+      </c>
+      <c r="J15" s="14">
+        <v>14.9</v>
+      </c>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="2">
+        <v>300.40325697386402</v>
+      </c>
+      <c r="G16" s="2">
+        <v>2.0020088120354602</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
+        <v>10</v>
+      </c>
+      <c r="J16" s="14">
+        <v>14.9</v>
+      </c>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="M1:P1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E288" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E287" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"default,RSE,NRSE,Differential,Pseudodifferential"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C288" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C287" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"no,yes"</formula1>
     </dataValidation>
   </dataValidations>

--- a/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
+++ b/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\School\Documents\data_gather\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\School\Documents\repos\DAQ\daq_system\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE3D888-3C9D-4681-816C-F704F57AC41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B1A567-788C-4B00-814C-5A73A82BC268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13" yWindow="0" windowWidth="25587" windowHeight="15267" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12720" yWindow="0" windowWidth="12960" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="112">
   <si>
     <t>Name</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>Dev5/ai20</t>
+  </si>
+  <si>
+    <t>Dev5/ai21</t>
+  </si>
+  <si>
+    <t>TC-HE-201</t>
   </si>
 </sst>
 </file>
@@ -974,7 +980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultColWidth="21.29296875" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="14.703125" style="2" customWidth="1"/>
@@ -1473,7 +1479,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A13" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>94</v>
@@ -1509,7 +1515,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>96</v>
@@ -1614,6 +1620,42 @@
       <c r="N16" s="14"/>
       <c r="O16" s="14"/>
       <c r="P16" s="14"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.5">
+      <c r="A17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="2">
+        <v>39.6</v>
+      </c>
+      <c r="G17" s="2">
+        <v>-292</v>
+      </c>
+      <c r="H17" s="14">
+        <v>2</v>
+      </c>
+      <c r="I17" s="15">
+        <v>10</v>
+      </c>
+      <c r="J17" s="14">
+        <v>52</v>
+      </c>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
+++ b/daq_system/inputs/CMS_Master_Data_Wiring_Dev5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\School\Documents\repos\DAQ\daq_system\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B1A567-788C-4B00-814C-5A73A82BC268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E17243-8B60-4F7D-96E9-0FCB1DFB77A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12720" yWindow="0" windowWidth="12960" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1073" yWindow="1073" windowWidth="19200" windowHeight="11720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="5" r:id="rId1"/>
